--- a/algstudent/s0/mesurements.xlsx
+++ b/algstudent/s0/mesurements.xlsx
@@ -1,65 +1,80 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27406"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\uo296503\Desktop\lab01\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C5132064-2BD5-48AF-B348-F4C39CD9B5C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12300"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="16">
+  <si>
+    <t>PythonA1.py (i7-4790,  8GB DDR3)</t>
+  </si>
+  <si>
+    <t>PythonA1.py (i5-13600kf, 32GB DDR5)</t>
+  </si>
   <si>
     <t>n</t>
   </si>
   <si>
+    <t>time(ms)</t>
+  </si>
+  <si>
+    <t>Java</t>
+  </si>
+  <si>
+    <t>times(ms)</t>
+  </si>
+  <si>
+    <t>18.0</t>
+  </si>
+  <si>
+    <t>49.0</t>
+  </si>
+  <si>
+    <t>183.0</t>
+  </si>
+  <si>
     <t>OoT</t>
   </si>
   <si>
-    <t>time(ms)</t>
-  </si>
-  <si>
-    <t>PythonA1.py (i7-4790,  8GB DDR3)</t>
-  </si>
-  <si>
-    <t>Java</t>
-  </si>
-  <si>
-    <t>times(ms)</t>
-  </si>
-  <si>
-    <t>18.0</t>
+    <t>688.0</t>
   </si>
   <si>
     <t>2638.0</t>
   </si>
   <si>
     <t>9939.0</t>
-  </si>
-  <si>
-    <t>49.0</t>
-  </si>
-  <si>
-    <t>183.0</t>
-  </si>
-  <si>
-    <t>688.0</t>
   </si>
   <si>
     <t>34498.0</t>
@@ -74,14 +89,20 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -92,7 +113,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -100,12 +121,238 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color theme="9"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color theme="9"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color theme="9"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color theme="9"/>
+      </right>
+      <top style="medium">
+        <color theme="9"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="9"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color theme="9"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="9"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color theme="9"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color theme="9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="5"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="5"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color theme="5"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="5"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color theme="5"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color theme="5"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color theme="5"/>
+      </right>
+      <top style="medium">
+        <color theme="5"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="5"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color theme="5"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="5"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="5"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="5"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="5"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="5"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color theme="5"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color theme="5"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -385,304 +632,716 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G32"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:O32"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="33.140625" customWidth="1"/>
+    <col min="9" max="9" width="33.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15">
       <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
+      <c r="B2" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="16" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="D2" s="17"/>
+      <c r="E2" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="E2" t="s">
+      <c r="G2" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="L2" s="5"/>
+      <c r="M2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F2" t="s">
-        <v>0</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="N2" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="O2" s="6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B3">
+    <row r="3" spans="1:15">
+      <c r="B3" s="19">
         <v>10000</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="13">
         <v>2499</v>
       </c>
-      <c r="F3">
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2">
         <v>10000</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="20" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B4">
+      <c r="J3" s="7">
+        <v>10000</v>
+      </c>
+      <c r="K3" s="2">
+        <v>1351</v>
+      </c>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2">
+        <v>10000</v>
+      </c>
+      <c r="O3" s="8">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
+      <c r="B4" s="19">
         <v>20000</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="13">
         <v>10972</v>
       </c>
-      <c r="F4">
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2">
         <v>20000</v>
       </c>
-      <c r="G4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B5">
+      <c r="G4" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="J4" s="7">
+        <v>20000</v>
+      </c>
+      <c r="K4" s="2">
+        <v>5540</v>
+      </c>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2">
+        <v>20000</v>
+      </c>
+      <c r="O4" s="8">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
+      <c r="B5" s="19">
         <v>40000</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="13">
         <v>41762</v>
       </c>
-      <c r="F5">
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2">
         <v>40000</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="J5" s="7">
+        <v>40000</v>
+      </c>
+      <c r="K5" s="2">
+        <v>22455</v>
+      </c>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2">
+        <v>40000</v>
+      </c>
+      <c r="O5" s="8">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="B6" s="19">
+        <v>80000</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2">
+        <v>80000</v>
+      </c>
+      <c r="G6" s="20" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B6">
+      <c r="J6" s="7">
         <v>80000</v>
       </c>
-      <c r="C6" t="s">
-        <v>1</v>
-      </c>
-      <c r="F6">
+      <c r="K6" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="L6" s="2"/>
+      <c r="M6" s="2"/>
+      <c r="N6" s="2">
         <v>80000</v>
       </c>
-      <c r="G6" t="s">
+      <c r="O6" s="8">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="B7" s="19">
+        <v>160000</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2">
+        <v>160000</v>
+      </c>
+      <c r="G7" s="20" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B7">
+      <c r="J7" s="7">
         <v>160000</v>
       </c>
-      <c r="C7" t="s">
-        <v>1</v>
-      </c>
-      <c r="F7">
+      <c r="K7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
+      <c r="N7" s="2">
         <v>160000</v>
       </c>
-      <c r="G7" t="s">
+      <c r="O7" s="8">
+        <v>1336</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="B8" s="19">
+        <v>320000</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2">
+        <v>320000</v>
+      </c>
+      <c r="G8" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="J8" s="7">
+        <v>320000</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
+      <c r="N8" s="2">
+        <v>320000</v>
+      </c>
+      <c r="O8" s="8">
+        <v>5028</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="B9" s="21">
+        <v>640000</v>
+      </c>
+      <c r="C9" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="23"/>
+      <c r="E9" s="23"/>
+      <c r="F9" s="23">
+        <v>640000</v>
+      </c>
+      <c r="G9" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="J9" s="9">
+        <v>640000</v>
+      </c>
+      <c r="K9" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="L9" s="11"/>
+      <c r="M9" s="11"/>
+      <c r="N9" s="11">
+        <v>640000</v>
+      </c>
+      <c r="O9" s="12">
+        <v>19054</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="C13" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="D13" s="17"/>
+      <c r="E13" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="F13" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="G13" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="K13" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="L13" s="5"/>
+      <c r="M13" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="N13" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="O13" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
+      <c r="B14" s="19">
+        <v>10000</v>
+      </c>
+      <c r="C14" s="2">
+        <v>285</v>
+      </c>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2">
+        <v>10000</v>
+      </c>
+      <c r="G14" s="20"/>
+      <c r="J14" s="7">
+        <v>10000</v>
+      </c>
+      <c r="K14" s="2">
+        <v>158</v>
+      </c>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2"/>
+      <c r="N14" s="2">
+        <v>10000</v>
+      </c>
+      <c r="O14" s="8">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B8">
+    <row r="15" spans="1:15">
+      <c r="B15" s="19">
+        <v>20000</v>
+      </c>
+      <c r="C15" s="2">
+        <v>1060</v>
+      </c>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2">
+        <v>20000</v>
+      </c>
+      <c r="G15" s="20"/>
+      <c r="J15" s="7">
+        <v>20000</v>
+      </c>
+      <c r="K15" s="2">
+        <v>593</v>
+      </c>
+      <c r="L15" s="2"/>
+      <c r="M15" s="2"/>
+      <c r="N15" s="2">
+        <v>20000</v>
+      </c>
+      <c r="O15" s="8">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15">
+      <c r="B16" s="19">
+        <v>40000</v>
+      </c>
+      <c r="C16" s="2">
+        <v>3909</v>
+      </c>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2">
+        <v>40000</v>
+      </c>
+      <c r="G16" s="20"/>
+      <c r="J16" s="7">
+        <v>40000</v>
+      </c>
+      <c r="K16" s="2">
+        <v>2236</v>
+      </c>
+      <c r="L16" s="2"/>
+      <c r="M16" s="2"/>
+      <c r="N16" s="2">
+        <v>40000</v>
+      </c>
+      <c r="O16" s="8">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15">
+      <c r="B17" s="19">
+        <v>80000</v>
+      </c>
+      <c r="C17" s="2">
+        <v>14703</v>
+      </c>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2">
+        <v>80000</v>
+      </c>
+      <c r="G17" s="20"/>
+      <c r="J17" s="7">
+        <v>80000</v>
+      </c>
+      <c r="K17" s="3">
+        <v>8424</v>
+      </c>
+      <c r="L17" s="2"/>
+      <c r="M17" s="2"/>
+      <c r="N17" s="2">
+        <v>80000</v>
+      </c>
+      <c r="O17" s="8">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15">
+      <c r="B18" s="19">
+        <v>160000</v>
+      </c>
+      <c r="C18" s="2">
+        <v>55852</v>
+      </c>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2">
+        <v>160000</v>
+      </c>
+      <c r="G18" s="20"/>
+      <c r="J18" s="7">
+        <v>160000</v>
+      </c>
+      <c r="K18" s="3">
+        <v>31744</v>
+      </c>
+      <c r="L18" s="2"/>
+      <c r="M18" s="2"/>
+      <c r="N18" s="2">
+        <v>160000</v>
+      </c>
+      <c r="O18" s="8">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15">
+      <c r="B19" s="19">
         <v>320000</v>
       </c>
-      <c r="C8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F8">
+      <c r="C19" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2">
         <v>320000</v>
       </c>
-      <c r="G8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B9">
+      <c r="G19" s="20"/>
+      <c r="J19" s="7">
+        <v>320000</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="L19" s="2"/>
+      <c r="M19" s="2"/>
+      <c r="N19" s="2">
+        <v>320000</v>
+      </c>
+      <c r="O19" s="8">
+        <v>5025</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15">
+      <c r="B20" s="21">
         <v>640000</v>
       </c>
-      <c r="C9" t="s">
-        <v>1</v>
-      </c>
-      <c r="F9">
+      <c r="C20" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20" s="23"/>
+      <c r="E20" s="23"/>
+      <c r="F20" s="23">
         <v>640000</v>
       </c>
-      <c r="G9" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="G20" s="24"/>
+      <c r="J20" s="9">
+        <v>640000</v>
+      </c>
+      <c r="K20" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="L20" s="11"/>
+      <c r="M20" s="11"/>
+      <c r="N20" s="11">
+        <v>640000</v>
+      </c>
+      <c r="O20" s="12">
+        <v>19023</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15">
+      <c r="A25" t="s">
+        <v>15</v>
+      </c>
+      <c r="B25" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="C25" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="D25" s="17"/>
+      <c r="E25" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="F25" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="G25" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="J25" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="K25" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="L25" s="5"/>
+      <c r="M25" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="N25" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="O25" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15">
+      <c r="B26" s="19">
+        <v>10000</v>
+      </c>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2">
+        <v>10000</v>
+      </c>
+      <c r="G26" s="20"/>
+      <c r="J26" s="7">
+        <v>10000</v>
+      </c>
+      <c r="K26" s="2">
+        <v>88</v>
+      </c>
+      <c r="L26" s="2"/>
+      <c r="M26" s="2"/>
+      <c r="N26" s="2">
+        <v>10000</v>
+      </c>
+      <c r="O26" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15">
+      <c r="B27" s="19">
+        <v>20000</v>
+      </c>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2">
+        <v>20000</v>
+      </c>
+      <c r="G27" s="20"/>
+      <c r="J27" s="7">
+        <v>20000</v>
+      </c>
+      <c r="K27" s="2">
+        <v>346</v>
+      </c>
+      <c r="L27" s="2"/>
+      <c r="M27" s="2"/>
+      <c r="N27" s="2">
+        <v>20000</v>
+      </c>
+      <c r="O27" s="8">
         <v>13</v>
       </c>
-      <c r="B13" t="s">
-        <v>0</v>
-      </c>
-      <c r="C13" t="s">
-        <v>5</v>
-      </c>
-      <c r="E13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F13" t="s">
-        <v>0</v>
-      </c>
-      <c r="G13" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B14">
-        <v>10000</v>
-      </c>
-      <c r="C14">
-        <v>285</v>
-      </c>
-      <c r="F14">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B15">
-        <v>20000</v>
-      </c>
-      <c r="C15">
-        <v>1060</v>
-      </c>
-      <c r="F15">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B16">
+    </row>
+    <row r="28" spans="1:15">
+      <c r="B28" s="19">
         <v>40000</v>
       </c>
-      <c r="C16">
-        <v>3909</v>
-      </c>
-      <c r="F16">
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2">
         <v>40000</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B17">
+      <c r="G28" s="20"/>
+      <c r="J28" s="7">
+        <v>40000</v>
+      </c>
+      <c r="K28" s="2">
+        <v>1318</v>
+      </c>
+      <c r="L28" s="2"/>
+      <c r="M28" s="2"/>
+      <c r="N28" s="2">
+        <v>40000</v>
+      </c>
+      <c r="O28" s="8">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15">
+      <c r="B29" s="19">
         <v>80000</v>
       </c>
-      <c r="C17">
-        <v>14703</v>
-      </c>
-      <c r="F17">
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2">
         <v>80000</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B18">
+      <c r="G29" s="20"/>
+      <c r="J29" s="7">
+        <v>80000</v>
+      </c>
+      <c r="K29" s="2">
+        <v>4922</v>
+      </c>
+      <c r="L29" s="2"/>
+      <c r="M29" s="2"/>
+      <c r="N29" s="2">
+        <v>80000</v>
+      </c>
+      <c r="O29" s="8">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15">
+      <c r="B30" s="19">
         <v>160000</v>
       </c>
-      <c r="C18">
-        <v>55852</v>
-      </c>
-      <c r="F18">
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2">
         <v>160000</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B19">
+      <c r="G30" s="20"/>
+      <c r="J30" s="7">
+        <v>160000</v>
+      </c>
+      <c r="K30" s="2">
+        <v>18507</v>
+      </c>
+      <c r="L30" s="2"/>
+      <c r="M30" s="2"/>
+      <c r="N30" s="2">
+        <v>160000</v>
+      </c>
+      <c r="O30" s="8">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15">
+      <c r="B31" s="19">
         <v>320000</v>
       </c>
-      <c r="C19" t="s">
-        <v>1</v>
-      </c>
-      <c r="F19">
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2">
         <v>320000</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B20">
+      <c r="G31" s="20"/>
+      <c r="J31" s="7">
+        <v>320000</v>
+      </c>
+      <c r="K31" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="L31" s="2"/>
+      <c r="M31" s="2"/>
+      <c r="N31" s="2">
+        <v>320000</v>
+      </c>
+      <c r="O31" s="8">
+        <v>2529</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15">
+      <c r="B32" s="21">
         <v>640000</v>
       </c>
-      <c r="C20" t="s">
-        <v>1</v>
-      </c>
-      <c r="F20">
+      <c r="C32" s="23"/>
+      <c r="D32" s="23"/>
+      <c r="E32" s="23"/>
+      <c r="F32" s="23">
         <v>640000</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>14</v>
-      </c>
-      <c r="B25" t="s">
-        <v>0</v>
-      </c>
-      <c r="C25" t="s">
-        <v>5</v>
-      </c>
-      <c r="E25" t="s">
-        <v>4</v>
-      </c>
-      <c r="F25" t="s">
-        <v>0</v>
-      </c>
-      <c r="G25" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B26">
-        <v>10000</v>
-      </c>
-      <c r="F26">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B27">
-        <v>20000</v>
-      </c>
-      <c r="F27">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B28">
-        <v>40000</v>
-      </c>
-      <c r="F28">
-        <v>40000</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B29">
-        <v>80000</v>
-      </c>
-      <c r="F29">
-        <v>80000</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B30">
-        <v>160000</v>
-      </c>
-      <c r="F30">
-        <v>160000</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B31">
-        <v>320000</v>
-      </c>
-      <c r="F31">
-        <v>320000</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B32">
+      <c r="G32" s="24"/>
+      <c r="J32" s="9">
         <v>640000</v>
       </c>
-      <c r="F32">
+      <c r="K32" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="L32" s="11"/>
+      <c r="M32" s="11"/>
+      <c r="N32" s="11">
         <v>640000</v>
+      </c>
+      <c r="O32" s="12">
+        <v>9569</v>
       </c>
     </row>
   </sheetData>
